--- a/artfynd/A 53944-2025 artfynd.xlsx
+++ b/artfynd/A 53944-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933322</v>
       </c>
       <c r="B2" t="n">
-        <v>106390</v>
+        <v>106396</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53944-2025 artfynd.xlsx
+++ b/artfynd/A 53944-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933322</v>
       </c>
       <c r="B2" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53944-2025 artfynd.xlsx
+++ b/artfynd/A 53944-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933322</v>
       </c>
       <c r="B2" t="n">
-        <v>106398</v>
+        <v>106399</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53944-2025 artfynd.xlsx
+++ b/artfynd/A 53944-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933322</v>
       </c>
       <c r="B2" t="n">
-        <v>106399</v>
+        <v>106405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53944-2025 artfynd.xlsx
+++ b/artfynd/A 53944-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933322</v>
       </c>
       <c r="B2" t="n">
-        <v>106405</v>
+        <v>106409</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53944-2025 artfynd.xlsx
+++ b/artfynd/A 53944-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933322</v>
       </c>
       <c r="B2" t="n">
-        <v>106409</v>
+        <v>106411</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53944-2025 artfynd.xlsx
+++ b/artfynd/A 53944-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933322</v>
       </c>
       <c r="B2" t="n">
-        <v>106411</v>
+        <v>106413</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53944-2025 artfynd.xlsx
+++ b/artfynd/A 53944-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933322</v>
       </c>
       <c r="B2" t="n">
-        <v>106413</v>
+        <v>106426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53944-2025 artfynd.xlsx
+++ b/artfynd/A 53944-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933322</v>
       </c>
       <c r="B2" t="n">
-        <v>106426</v>
+        <v>106428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53944-2025 artfynd.xlsx
+++ b/artfynd/A 53944-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933322</v>
       </c>
       <c r="B2" t="n">
-        <v>106428</v>
+        <v>106432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53944-2025 artfynd.xlsx
+++ b/artfynd/A 53944-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933322</v>
       </c>
       <c r="B2" t="n">
-        <v>106432</v>
+        <v>106451</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53944-2025 artfynd.xlsx
+++ b/artfynd/A 53944-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933322</v>
       </c>
       <c r="B2" t="n">
-        <v>106451</v>
+        <v>106452</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53944-2025 artfynd.xlsx
+++ b/artfynd/A 53944-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933322</v>
       </c>
       <c r="B2" t="n">
-        <v>106452</v>
+        <v>106457</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53944-2025 artfynd.xlsx
+++ b/artfynd/A 53944-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933322</v>
       </c>
       <c r="B2" t="n">
-        <v>106457</v>
+        <v>106460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53944-2025 artfynd.xlsx
+++ b/artfynd/A 53944-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933322</v>
       </c>
       <c r="B2" t="n">
-        <v>106460</v>
+        <v>106466</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53944-2025 artfynd.xlsx
+++ b/artfynd/A 53944-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933322</v>
       </c>
       <c r="B2" t="n">
-        <v>106466</v>
+        <v>106467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53944-2025 artfynd.xlsx
+++ b/artfynd/A 53944-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933322</v>
       </c>
       <c r="B2" t="n">
-        <v>106467</v>
+        <v>106479</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53944-2025 artfynd.xlsx
+++ b/artfynd/A 53944-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933322</v>
       </c>
       <c r="B2" t="n">
-        <v>106479</v>
+        <v>106480</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53944-2025 artfynd.xlsx
+++ b/artfynd/A 53944-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933322</v>
       </c>
       <c r="B2" t="n">
-        <v>106480</v>
+        <v>106483</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53944-2025 artfynd.xlsx
+++ b/artfynd/A 53944-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933322</v>
       </c>
       <c r="B2" t="n">
-        <v>106483</v>
+        <v>106485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53944-2025 artfynd.xlsx
+++ b/artfynd/A 53944-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933322</v>
       </c>
       <c r="B2" t="n">
-        <v>106485</v>
+        <v>106489</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
